--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC17B0E-A460-4A21-B783-838378C4A0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C97A2FA-5950-444A-9ABB-597E4B558AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7C508D13-737D-4794-A4CB-EC4BF750435B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F58464AA-9741-44DC-9DE3-C4BCB80A24FC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1108,7 +1108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9348BA-A6A0-4AD5-9E60-26286184A555}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EE9C4E-DAA6-41B7-BABE-776109108A53}">
   <dimension ref="B3:L78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C97A2FA-5950-444A-9ABB-597E4B558AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C7C2C67-D477-4C0D-9246-C1E587ADA9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F58464AA-9741-44DC-9DE3-C4BCB80A24FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{868AA0B5-A579-4FEA-8C38-6B70F906F753}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1108,7 +1108,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EE9C4E-DAA6-41B7-BABE-776109108A53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F78627-4AEE-41B2-8426-03F3C8AFADF7}">
   <dimension ref="B3:L78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C7C2C67-D477-4C0D-9246-C1E587ADA9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{486A6B83-4DE9-43CD-9EC4-035299CF9F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{868AA0B5-A579-4FEA-8C38-6B70F906F753}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7843E4D3-216F-4B57-A796-5B5A5324A5D4}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="238">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -134,6 +134,9 @@
     <t>g_sol1-dem3</t>
   </si>
   <si>
+    <t>g_sol1-gen4</t>
+  </si>
+  <si>
     <t>e_sol10</t>
   </si>
   <si>
@@ -236,9 +239,6 @@
     <t>e_sol4</t>
   </si>
   <si>
-    <t>g_sol4-dem3</t>
-  </si>
-  <si>
     <t>g_sol4-gen4</t>
   </si>
   <si>
@@ -251,6 +251,9 @@
     <t>e_sol6</t>
   </si>
   <si>
+    <t>g_sol6-dem1</t>
+  </si>
+  <si>
     <t>g_sol6-gen4</t>
   </si>
   <si>
@@ -266,6 +269,9 @@
     <t>g_sol8-dem1</t>
   </si>
   <si>
+    <t>g_sol8-dem4</t>
+  </si>
+  <si>
     <t>e_sol9</t>
   </si>
   <si>
@@ -548,6 +554,9 @@
     <t>grid link -75.0 km- Renewable cluster 1 to Demand cluster 3</t>
   </si>
   <si>
+    <t>grid link -81.0 km- Renewable cluster 1 to Generation cluster 4</t>
+  </si>
+  <si>
     <t>grid link -29.0 km- Potential connection: Renewable cluster 10 to Generation cluster 3</t>
   </si>
   <si>
@@ -578,7 +587,7 @@
     <t>grid link -155.0 km- Renewable cluster 19 to Demand cluster 4</t>
   </si>
   <si>
-    <t>grid link -33.0 km- Potential connection: Renewable cluster 2 to Demand cluster 3</t>
+    <t>grid link -33.0 km- Renewable cluster 2 to Demand cluster 3</t>
   </si>
   <si>
     <t>grid link -105.0 km- Renewable cluster 20 to Demand cluster 4</t>
@@ -599,15 +608,15 @@
     <t>grid link -190.0 km- Renewable cluster 3 to Generation cluster 4</t>
   </si>
   <si>
-    <t>grid link -106.0 km- Renewable cluster 4 to Demand cluster 3</t>
-  </si>
-  <si>
     <t>grid link -157.0 km- Renewable cluster 4 to Generation cluster 4</t>
   </si>
   <si>
     <t>grid link -172.0 km- Potential connection: Renewable cluster 5 to Generation cluster 4</t>
   </si>
   <si>
+    <t>grid link -200.0 km- Renewable cluster 6 to Demand cluster 1</t>
+  </si>
+  <si>
     <t>grid link -52.0 km- Renewable cluster 6 to Generation cluster 4</t>
   </si>
   <si>
@@ -615,6 +624,9 @@
   </si>
   <si>
     <t>grid link -203.0 km- Renewable cluster 8 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -246.0 km- Renewable cluster 8 to Demand cluster 4</t>
   </si>
   <si>
     <t>grid link -136.0 km- Potential connection: Renewable cluster 9 to Generation cluster 1</t>
@@ -1108,8 +1120,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F78627-4AEE-41B2-8426-03F3C8AFADF7}">
-  <dimension ref="B3:L78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED2EA76-4B07-41C3-B765-97A517369777}">
+  <dimension ref="B3:L80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -1117,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -1143,10 +1155,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -1175,7 +1187,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -1204,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -1233,7 +1245,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -1262,7 +1274,7 @@
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -1291,7 +1303,7 @@
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -1320,7 +1332,7 @@
         <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -1349,7 +1361,7 @@
         <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -1378,7 +1390,7 @@
         <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -1407,7 +1419,7 @@
         <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -1436,7 +1448,7 @@
         <v>31</v>
       </c>
       <c r="L14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -1450,22 +1462,22 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" t="s">
-        <v>33</v>
-      </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -1479,22 +1491,22 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -1508,22 +1520,22 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" t="s">
         <v>36</v>
       </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" t="s">
-        <v>37</v>
-      </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -1537,22 +1549,22 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
         <v>38</v>
       </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -1566,22 +1578,22 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
         <v>40</v>
       </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -1595,22 +1607,22 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -1624,22 +1636,22 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
         <v>44</v>
       </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
-        <v>45</v>
-      </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -1653,22 +1665,22 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
         <v>46</v>
       </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
-      </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -1682,22 +1694,22 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
         <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -1711,22 +1723,22 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
         <v>50</v>
       </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
       <c r="K24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -1740,22 +1752,22 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" t="s">
-        <v>53</v>
-      </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -1769,22 +1781,22 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>55</v>
-      </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -1798,22 +1810,22 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -1827,22 +1839,22 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
         <v>58</v>
       </c>
-      <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" t="s">
-        <v>59</v>
-      </c>
       <c r="H28" t="s">
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -1856,22 +1868,22 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" t="s">
         <v>60</v>
       </c>
-      <c r="F29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>61</v>
-      </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -1885,22 +1897,22 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" t="s">
         <v>62</v>
       </c>
-      <c r="F30" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" t="s">
-        <v>63</v>
-      </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -1914,10 +1926,10 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
         <v>64</v>
@@ -1929,7 +1941,7 @@
         <v>64</v>
       </c>
       <c r="L31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -1943,22 +1955,22 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
         <v>65</v>
       </c>
-      <c r="F32" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" t="s">
-        <v>66</v>
-      </c>
       <c r="H32" t="s">
         <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -1972,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
@@ -1987,7 +1999,7 @@
         <v>67</v>
       </c>
       <c r="L33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -2016,7 +2028,7 @@
         <v>69</v>
       </c>
       <c r="L34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -2033,7 +2045,7 @@
         <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
         <v>71</v>
@@ -2045,7 +2057,7 @@
         <v>71</v>
       </c>
       <c r="L35" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -2059,22 +2071,22 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L36" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -2088,22 +2100,22 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" t="s">
         <v>74</v>
       </c>
-      <c r="F37" t="s">
-        <v>17</v>
-      </c>
-      <c r="G37" t="s">
-        <v>75</v>
-      </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L37" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -2117,22 +2129,22 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" t="s">
         <v>76</v>
       </c>
-      <c r="F38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" t="s">
-        <v>77</v>
-      </c>
       <c r="H38" t="s">
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -2146,22 +2158,22 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -2175,22 +2187,22 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L40" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -2204,22 +2216,22 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -2233,22 +2245,22 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -2262,22 +2274,22 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L43" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -2291,22 +2303,22 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L44" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -2320,22 +2332,22 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -2349,22 +2361,22 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -2378,22 +2390,22 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L47" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -2407,22 +2419,22 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L48" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -2436,22 +2448,22 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -2465,22 +2477,22 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L50" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -2494,22 +2506,22 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L51" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -2523,22 +2535,22 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L52" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -2552,22 +2564,22 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -2581,22 +2593,22 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -2610,22 +2622,22 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -2639,22 +2651,22 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -2668,22 +2680,22 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H57" t="s">
         <v>13</v>
       </c>
       <c r="K57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L57" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -2697,22 +2709,22 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L58" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -2726,22 +2738,22 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
       </c>
       <c r="K59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L59" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.45">
@@ -2755,22 +2767,22 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
       </c>
       <c r="K60" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L60" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.45">
@@ -2784,22 +2796,22 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L61" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.45">
@@ -2816,19 +2828,19 @@
         <v>122</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
       </c>
       <c r="K62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L62" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.45">
@@ -2842,22 +2854,22 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" t="s">
         <v>125</v>
       </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" t="s">
-        <v>126</v>
-      </c>
       <c r="H63" t="s">
         <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L63" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.45">
@@ -2871,22 +2883,22 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F64" t="s">
         <v>10</v>
       </c>
       <c r="G64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
       </c>
       <c r="K64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.45">
@@ -2900,22 +2912,22 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
         <v>10</v>
       </c>
       <c r="G65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H65" t="s">
         <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.45">
@@ -2929,22 +2941,22 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
       </c>
       <c r="K66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.45">
@@ -2958,22 +2970,22 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G67" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L67" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.45">
@@ -2987,22 +2999,22 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F68" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
       </c>
       <c r="K68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.45">
@@ -3016,22 +3028,22 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F69" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G69" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.45">
@@ -3045,22 +3057,22 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F70" t="s">
         <v>21</v>
       </c>
       <c r="G70" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H70" t="s">
         <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.45">
@@ -3074,22 +3086,22 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L71" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.45">
@@ -3103,22 +3115,22 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
       </c>
       <c r="K72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L72" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.45">
@@ -3132,22 +3144,22 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F73" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L73" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.45">
@@ -3161,22 +3173,22 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
       </c>
       <c r="K74" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L74" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.45">
@@ -3190,22 +3202,22 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G75" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L75" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.45">
@@ -3219,22 +3231,22 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.45">
@@ -3248,22 +3260,22 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L77" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="2:12" x14ac:dyDescent="0.45">
@@ -3277,22 +3289,80 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="G78" t="s">
+        <v>154</v>
+      </c>
+      <c r="H78" t="s">
+        <v>13</v>
+      </c>
+      <c r="K78" t="s">
+        <v>154</v>
+      </c>
+      <c r="L78" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>155</v>
+      </c>
+      <c r="F79" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" t="s">
         <v>156</v>
       </c>
-      <c r="H78" t="s">
-        <v>13</v>
-      </c>
-      <c r="K78" t="s">
+      <c r="H79" t="s">
+        <v>13</v>
+      </c>
+      <c r="K79" t="s">
         <v>156</v>
       </c>
-      <c r="L78" t="s">
-        <v>233</v>
+      <c r="L79" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" t="s">
+        <v>157</v>
+      </c>
+      <c r="F80" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" t="s">
+        <v>13</v>
+      </c>
+      <c r="K80" t="s">
+        <v>158</v>
+      </c>
+      <c r="L80" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{486A6B83-4DE9-43CD-9EC4-035299CF9F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8D8C61C-1FFD-4CD0-AE30-6999962C81EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7843E4D3-216F-4B57-A796-5B5A5324A5D4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E6C1D98F-23EA-4F17-A028-CBE2C29670BD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="133">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -278,138 +278,12 @@
     <t>g_sol9-gen1</t>
   </si>
   <si>
-    <t>e_wof0</t>
-  </si>
-  <si>
-    <t>g_wof0-dem0</t>
-  </si>
-  <si>
-    <t>e_wof1</t>
-  </si>
-  <si>
-    <t>g_wof1-gen0</t>
-  </si>
-  <si>
-    <t>e_wof10</t>
-  </si>
-  <si>
-    <t>g_wof10-dem3</t>
-  </si>
-  <si>
-    <t>e_wof11</t>
-  </si>
-  <si>
-    <t>g_wof11-dem3</t>
-  </si>
-  <si>
-    <t>e_wof12</t>
-  </si>
-  <si>
-    <t>g_wof12-dem4</t>
-  </si>
-  <si>
-    <t>e_wof13</t>
-  </si>
-  <si>
-    <t>g_wof13-dem0</t>
-  </si>
-  <si>
-    <t>e_wof14</t>
-  </si>
-  <si>
-    <t>g_wof14-gen2</t>
-  </si>
-  <si>
-    <t>e_wof15</t>
-  </si>
-  <si>
-    <t>g_wof15-gen2</t>
-  </si>
-  <si>
-    <t>e_wof16</t>
-  </si>
-  <si>
-    <t>g_wof16-gen3</t>
-  </si>
-  <si>
-    <t>e_wof17</t>
-  </si>
-  <si>
-    <t>g_wof17-dem0</t>
-  </si>
-  <si>
-    <t>e_wof18</t>
-  </si>
-  <si>
-    <t>g_wof18-gen2</t>
-  </si>
-  <si>
-    <t>e_wof19</t>
-  </si>
-  <si>
-    <t>g_wof19-gen2</t>
-  </si>
-  <si>
-    <t>e_wof2</t>
-  </si>
-  <si>
-    <t>g_wof2-gen1</t>
-  </si>
-  <si>
-    <t>e_wof3</t>
-  </si>
-  <si>
-    <t>g_wof3-dem2</t>
-  </si>
-  <si>
-    <t>e_wof4</t>
-  </si>
-  <si>
-    <t>g_wof4-dem2</t>
-  </si>
-  <si>
-    <t>e_wof5</t>
-  </si>
-  <si>
-    <t>g_wof5-dem2</t>
-  </si>
-  <si>
-    <t>e_wof6</t>
-  </si>
-  <si>
-    <t>g_wof6-gen3</t>
-  </si>
-  <si>
-    <t>e_wof7</t>
-  </si>
-  <si>
-    <t>g_wof7-gen3</t>
-  </si>
-  <si>
-    <t>e_wof8</t>
-  </si>
-  <si>
-    <t>g_wof8-dem4</t>
-  </si>
-  <si>
-    <t>e_wof9</t>
-  </si>
-  <si>
-    <t>g_wof9-gen1</t>
-  </si>
-  <si>
     <t>e_won0</t>
   </si>
   <si>
     <t>g_won0-gen1</t>
   </si>
   <si>
-    <t>e_won1</t>
-  </si>
-  <si>
-    <t>g_won1-dem1</t>
-  </si>
-  <si>
     <t>e_won10</t>
   </si>
   <si>
@@ -419,102 +293,18 @@
     <t>g_won10-gen0</t>
   </si>
   <si>
-    <t>e_won11</t>
-  </si>
-  <si>
-    <t>g_won11-gen0</t>
-  </si>
-  <si>
-    <t>e_won12</t>
-  </si>
-  <si>
-    <t>g_won12-gen0</t>
-  </si>
-  <si>
-    <t>e_won13</t>
-  </si>
-  <si>
-    <t>g_won13-gen0</t>
-  </si>
-  <si>
-    <t>e_won14</t>
-  </si>
-  <si>
-    <t>g_won14-dem4</t>
-  </si>
-  <si>
-    <t>e_won15</t>
-  </si>
-  <si>
-    <t>g_won15-gen3</t>
-  </si>
-  <si>
     <t>e_won16</t>
   </si>
   <si>
     <t>g_won16-dem0</t>
   </si>
   <si>
-    <t>e_won17</t>
-  </si>
-  <si>
-    <t>g_won17-dem0</t>
-  </si>
-  <si>
-    <t>e_won18</t>
-  </si>
-  <si>
-    <t>g_won18-dem0</t>
-  </si>
-  <si>
-    <t>e_won2</t>
-  </si>
-  <si>
-    <t>g_won2-gen1</t>
-  </si>
-  <si>
-    <t>e_won3</t>
-  </si>
-  <si>
-    <t>g_won3-gen1</t>
-  </si>
-  <si>
-    <t>e_won4</t>
-  </si>
-  <si>
-    <t>g_won4-dem3</t>
-  </si>
-  <si>
     <t>e_won5</t>
   </si>
   <si>
     <t>g_won5-dem1</t>
   </si>
   <si>
-    <t>e_won6</t>
-  </si>
-  <si>
-    <t>g_won6-gen1</t>
-  </si>
-  <si>
-    <t>e_won7</t>
-  </si>
-  <si>
-    <t>g_won7-gen1</t>
-  </si>
-  <si>
-    <t>e_won8</t>
-  </si>
-  <si>
-    <t>g_won8-gen1</t>
-  </si>
-  <si>
-    <t>e_won9</t>
-  </si>
-  <si>
-    <t>g_won9-gen1</t>
-  </si>
-  <si>
     <t>~tradelinks_desc</t>
   </si>
   <si>
@@ -530,10 +320,10 @@
     <t>grid link -301.0 km- Generation cluster 0 to Demand cluster 4</t>
   </si>
   <si>
-    <t>grid link -143.0 km- Generation cluster 1 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -236.0 km- Generation cluster 1 to Demand cluster 4</t>
+    <t>grid link -137.0 km- Generation cluster 1 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -243.0 km- Generation cluster 1 to Demand cluster 4</t>
   </si>
   <si>
     <t>grid link -72.0 km- Generation cluster 2 to Demand cluster 0</t>
@@ -599,7 +389,7 @@
     <t>grid link -24.0 km- Potential connection: Renewable cluster 22 to Demand cluster 1</t>
   </si>
   <si>
-    <t>grid link -51.0 km- Potential connection: Renewable cluster 23 to Generation cluster 1</t>
+    <t>grid link -53.0 km- Potential connection: Renewable cluster 23 to Generation cluster 1</t>
   </si>
   <si>
     <t>grid link -146.0 km- Renewable cluster 3 to Demand cluster 3</t>
@@ -629,127 +419,22 @@
     <t>grid link -246.0 km- Renewable cluster 8 to Demand cluster 4</t>
   </si>
   <si>
-    <t>grid link -136.0 km- Potential connection: Renewable cluster 9 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -200.0 km- Potential connection: Renewable cluster 43 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -226.0 km- Potential connection: Renewable cluster 44 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -210.0 km- Potential connection: Renewable cluster 53 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -136.0 km- Potential connection: Renewable cluster 54 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -104.0 km- Potential connection: Renewable cluster 55 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -142.0 km- Potential connection: Renewable cluster 56 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -124.0 km- Potential connection: Renewable cluster 57 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -218.0 km- Potential connection: Renewable cluster 58 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -124.0 km- Potential connection: Renewable cluster 59 to Generation cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -139.0 km- Potential connection: Renewable cluster 60 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -218.0 km- Potential connection: Renewable cluster 61 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -122.0 km- Potential connection: Renewable cluster 62 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -154.0 km- Potential connection: Renewable cluster 45 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -111.0 km- Potential connection: Renewable cluster 46 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -200.0 km- Potential connection: Renewable cluster 47 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -148.0 km- Potential connection: Renewable cluster 48 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -110.0 km- Potential connection: Renewable cluster 49 to Generation cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -112.0 km- Potential connection: Renewable cluster 50 to Generation cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -138.0 km- Potential connection: Renewable cluster 51 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -215.0 km- Potential connection: Renewable cluster 52 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- Potential connection: Renewable cluster 24 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -143.0 km- Potential connection: Renewable cluster 25 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -199.0 km- Renewable cluster 34 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -185.0 km- Renewable cluster 34 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -5.0 km- Potential connection: Renewable cluster 35 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -111.0 km- Potential connection: Renewable cluster 36 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -135.0 km- Potential connection: Renewable cluster 37 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -19.0 km- Potential connection: Renewable cluster 38 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -18.0 km- Potential connection: Renewable cluster 39 to Generation cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- Renewable cluster 40 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -18.0 km- Potential connection: Renewable cluster 41 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -122.0 km- Potential connection: Renewable cluster 42 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -170.0 km- Potential connection: Renewable cluster 26 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -126.0 km- Potential connection: Renewable cluster 27 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -79.0 km- Potential connection: Renewable cluster 28 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -147.0 km- Renewable cluster 29 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- Potential connection: Renewable cluster 30 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -37.0 km- Potential connection: Renewable cluster 31 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -114.0 km- Potential connection: Renewable cluster 32 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -37.0 km- Potential connection: Renewable cluster 33 to Generation cluster 1</t>
+    <t>grid link -137.0 km- Potential connection: Renewable cluster 9 to Generation cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -72.0 km- Potential connection: Renewable cluster 24 to Generation cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 34 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 34 to Generation cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 40 to Demand cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 29 to Demand cluster 1</t>
   </si>
 </sst>
 </file>
@@ -1120,8 +805,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED2EA76-4B07-41C3-B765-97A517369777}">
-  <dimension ref="B3:L80"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11784C7-CD43-430C-BE28-3DBFF61ED80E}">
+  <dimension ref="B3:L45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -1129,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -1155,10 +840,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -1187,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -1216,7 +901,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -1245,7 +930,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -1274,7 +959,7 @@
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>165</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -1303,7 +988,7 @@
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -1332,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -1361,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>168</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -1390,7 +1075,7 @@
         <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>169</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -1419,7 +1104,7 @@
         <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -1448,7 +1133,7 @@
         <v>31</v>
       </c>
       <c r="L14" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -1477,7 +1162,7 @@
         <v>32</v>
       </c>
       <c r="L15" t="s">
-        <v>172</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -1506,7 +1191,7 @@
         <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>173</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -1535,7 +1220,7 @@
         <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -1564,7 +1249,7 @@
         <v>38</v>
       </c>
       <c r="L18" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -1593,7 +1278,7 @@
         <v>40</v>
       </c>
       <c r="L19" t="s">
-        <v>176</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -1622,7 +1307,7 @@
         <v>42</v>
       </c>
       <c r="L20" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -1651,7 +1336,7 @@
         <v>44</v>
       </c>
       <c r="L21" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -1680,7 +1365,7 @@
         <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -1709,7 +1394,7 @@
         <v>48</v>
       </c>
       <c r="L23" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -1738,7 +1423,7 @@
         <v>50</v>
       </c>
       <c r="L24" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -1767,7 +1452,7 @@
         <v>52</v>
       </c>
       <c r="L25" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -1796,7 +1481,7 @@
         <v>54</v>
       </c>
       <c r="L26" t="s">
-        <v>183</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -1825,7 +1510,7 @@
         <v>56</v>
       </c>
       <c r="L27" t="s">
-        <v>184</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -1854,7 +1539,7 @@
         <v>58</v>
       </c>
       <c r="L28" t="s">
-        <v>185</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -1883,7 +1568,7 @@
         <v>60</v>
       </c>
       <c r="L29" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -1912,7 +1597,7 @@
         <v>62</v>
       </c>
       <c r="L30" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -1941,7 +1626,7 @@
         <v>64</v>
       </c>
       <c r="L31" t="s">
-        <v>188</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -1970,7 +1655,7 @@
         <v>65</v>
       </c>
       <c r="L32" t="s">
-        <v>189</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -1999,7 +1684,7 @@
         <v>67</v>
       </c>
       <c r="L33" t="s">
-        <v>190</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -2028,7 +1713,7 @@
         <v>69</v>
       </c>
       <c r="L34" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -2057,7 +1742,7 @@
         <v>71</v>
       </c>
       <c r="L35" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -2086,7 +1771,7 @@
         <v>72</v>
       </c>
       <c r="L36" t="s">
-        <v>193</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -2115,7 +1800,7 @@
         <v>74</v>
       </c>
       <c r="L37" t="s">
-        <v>194</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -2144,7 +1829,7 @@
         <v>76</v>
       </c>
       <c r="L38" t="s">
-        <v>195</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -2173,7 +1858,7 @@
         <v>77</v>
       </c>
       <c r="L39" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -2202,7 +1887,7 @@
         <v>79</v>
       </c>
       <c r="L40" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -2219,7 +1904,7 @@
         <v>80</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
         <v>81</v>
@@ -2231,7 +1916,7 @@
         <v>81</v>
       </c>
       <c r="L41" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -2248,7 +1933,7 @@
         <v>82</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
         <v>83</v>
@@ -2260,7 +1945,7 @@
         <v>83</v>
       </c>
       <c r="L42" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -2274,22 +1959,22 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
         <v>84</v>
       </c>
-      <c r="F43" t="s">
-        <v>28</v>
-      </c>
-      <c r="G43" t="s">
-        <v>85</v>
-      </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L43" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -2303,22 +1988,22 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
         <v>86</v>
       </c>
-      <c r="F44" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44" t="s">
-        <v>87</v>
-      </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L44" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -2332,1037 +2017,22 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" t="s">
         <v>88</v>
       </c>
-      <c r="F45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" t="s">
-        <v>89</v>
-      </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L45" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s">
-        <v>90</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" t="s">
-        <v>91</v>
-      </c>
-      <c r="L46" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>92</v>
-      </c>
-      <c r="F47" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" t="s">
-        <v>93</v>
-      </c>
-      <c r="L47" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>95</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-      <c r="K48" t="s">
-        <v>95</v>
-      </c>
-      <c r="L48" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" t="s">
-        <v>96</v>
-      </c>
-      <c r="F49" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" t="s">
-        <v>97</v>
-      </c>
-      <c r="L49" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" t="s">
-        <v>98</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" t="s">
-        <v>99</v>
-      </c>
-      <c r="H50" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" t="s">
-        <v>99</v>
-      </c>
-      <c r="L50" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" t="s">
-        <v>101</v>
-      </c>
-      <c r="H51" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" t="s">
-        <v>101</v>
-      </c>
-      <c r="L51" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" t="s">
-        <v>102</v>
-      </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" t="s">
-        <v>103</v>
-      </c>
-      <c r="H52" t="s">
-        <v>13</v>
-      </c>
-      <c r="K52" t="s">
-        <v>103</v>
-      </c>
-      <c r="L52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>104</v>
-      </c>
-      <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" t="s">
-        <v>105</v>
-      </c>
-      <c r="H53" t="s">
-        <v>13</v>
-      </c>
-      <c r="K53" t="s">
-        <v>105</v>
-      </c>
-      <c r="L53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" t="s">
-        <v>106</v>
-      </c>
-      <c r="F54" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" t="s">
-        <v>107</v>
-      </c>
-      <c r="H54" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" t="s">
-        <v>107</v>
-      </c>
-      <c r="L54" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>108</v>
-      </c>
-      <c r="F55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55" t="s">
-        <v>109</v>
-      </c>
-      <c r="H55" t="s">
-        <v>13</v>
-      </c>
-      <c r="K55" t="s">
-        <v>109</v>
-      </c>
-      <c r="L55" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56" t="s">
-        <v>111</v>
-      </c>
-      <c r="H56" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" t="s">
-        <v>111</v>
-      </c>
-      <c r="L56" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>112</v>
-      </c>
-      <c r="F57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>113</v>
-      </c>
-      <c r="H57" t="s">
-        <v>13</v>
-      </c>
-      <c r="K57" t="s">
-        <v>113</v>
-      </c>
-      <c r="L57" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>114</v>
-      </c>
-      <c r="F58" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
-        <v>115</v>
-      </c>
-      <c r="H58" t="s">
-        <v>13</v>
-      </c>
-      <c r="K58" t="s">
-        <v>115</v>
-      </c>
-      <c r="L58" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>116</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>117</v>
-      </c>
-      <c r="H59" t="s">
-        <v>13</v>
-      </c>
-      <c r="K59" t="s">
-        <v>117</v>
-      </c>
-      <c r="L59" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>118</v>
-      </c>
-      <c r="F60" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" t="s">
-        <v>119</v>
-      </c>
-      <c r="H60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K60" t="s">
-        <v>119</v>
-      </c>
-      <c r="L60" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>120</v>
-      </c>
-      <c r="F61" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" t="s">
-        <v>121</v>
-      </c>
-      <c r="H61" t="s">
-        <v>13</v>
-      </c>
-      <c r="K61" t="s">
-        <v>121</v>
-      </c>
-      <c r="L61" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" t="s">
-        <v>122</v>
-      </c>
-      <c r="F62" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" t="s">
-        <v>123</v>
-      </c>
-      <c r="H62" t="s">
-        <v>13</v>
-      </c>
-      <c r="K62" t="s">
-        <v>123</v>
-      </c>
-      <c r="L62" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>124</v>
-      </c>
-      <c r="F63" t="s">
-        <v>11</v>
-      </c>
-      <c r="G63" t="s">
-        <v>125</v>
-      </c>
-      <c r="H63" t="s">
-        <v>13</v>
-      </c>
-      <c r="K63" t="s">
-        <v>125</v>
-      </c>
-      <c r="L63" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" t="s">
-        <v>124</v>
-      </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" t="s">
-        <v>126</v>
-      </c>
-      <c r="H64" t="s">
-        <v>13</v>
-      </c>
-      <c r="K64" t="s">
-        <v>126</v>
-      </c>
-      <c r="L64" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" t="s">
-        <v>127</v>
-      </c>
-      <c r="F65" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" t="s">
-        <v>128</v>
-      </c>
-      <c r="H65" t="s">
-        <v>13</v>
-      </c>
-      <c r="K65" t="s">
-        <v>128</v>
-      </c>
-      <c r="L65" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" t="s">
-        <v>129</v>
-      </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" t="s">
-        <v>130</v>
-      </c>
-      <c r="H66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K66" t="s">
-        <v>130</v>
-      </c>
-      <c r="L66" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>131</v>
-      </c>
-      <c r="F67" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" t="s">
         <v>132</v>
-      </c>
-      <c r="H67" t="s">
-        <v>13</v>
-      </c>
-      <c r="K67" t="s">
-        <v>132</v>
-      </c>
-      <c r="L67" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B68" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" t="s">
-        <v>133</v>
-      </c>
-      <c r="F68" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" t="s">
-        <v>134</v>
-      </c>
-      <c r="H68" t="s">
-        <v>13</v>
-      </c>
-      <c r="K68" t="s">
-        <v>134</v>
-      </c>
-      <c r="L68" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B69" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
-        <v>135</v>
-      </c>
-      <c r="F69" t="s">
-        <v>24</v>
-      </c>
-      <c r="G69" t="s">
-        <v>136</v>
-      </c>
-      <c r="H69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K69" t="s">
-        <v>136</v>
-      </c>
-      <c r="L69" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B70" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" t="s">
-        <v>137</v>
-      </c>
-      <c r="F70" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70" t="s">
-        <v>138</v>
-      </c>
-      <c r="H70" t="s">
-        <v>13</v>
-      </c>
-      <c r="K70" t="s">
-        <v>138</v>
-      </c>
-      <c r="L70" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B71" t="s">
-        <v>8</v>
-      </c>
-      <c r="C71" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" t="s">
-        <v>139</v>
-      </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" t="s">
-        <v>140</v>
-      </c>
-      <c r="H71" t="s">
-        <v>13</v>
-      </c>
-      <c r="K71" t="s">
-        <v>140</v>
-      </c>
-      <c r="L71" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B72" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" t="s">
-        <v>141</v>
-      </c>
-      <c r="F72" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" t="s">
-        <v>142</v>
-      </c>
-      <c r="H72" t="s">
-        <v>13</v>
-      </c>
-      <c r="K72" t="s">
-        <v>142</v>
-      </c>
-      <c r="L72" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B73" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" t="s">
-        <v>143</v>
-      </c>
-      <c r="F73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" t="s">
-        <v>144</v>
-      </c>
-      <c r="H73" t="s">
-        <v>13</v>
-      </c>
-      <c r="K73" t="s">
-        <v>144</v>
-      </c>
-      <c r="L73" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B74" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" t="s">
-        <v>145</v>
-      </c>
-      <c r="F74" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" t="s">
-        <v>146</v>
-      </c>
-      <c r="H74" t="s">
-        <v>13</v>
-      </c>
-      <c r="K74" t="s">
-        <v>146</v>
-      </c>
-      <c r="L74" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B75" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" t="s">
-        <v>147</v>
-      </c>
-      <c r="F75" t="s">
-        <v>28</v>
-      </c>
-      <c r="G75" t="s">
-        <v>148</v>
-      </c>
-      <c r="H75" t="s">
-        <v>13</v>
-      </c>
-      <c r="K75" t="s">
-        <v>148</v>
-      </c>
-      <c r="L75" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B76" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>149</v>
-      </c>
-      <c r="F76" t="s">
-        <v>17</v>
-      </c>
-      <c r="G76" t="s">
-        <v>150</v>
-      </c>
-      <c r="H76" t="s">
-        <v>13</v>
-      </c>
-      <c r="K76" t="s">
-        <v>150</v>
-      </c>
-      <c r="L76" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B77" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>151</v>
-      </c>
-      <c r="F77" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s">
-        <v>152</v>
-      </c>
-      <c r="H77" t="s">
-        <v>13</v>
-      </c>
-      <c r="K77" t="s">
-        <v>152</v>
-      </c>
-      <c r="L77" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B78" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>153</v>
-      </c>
-      <c r="F78" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" t="s">
-        <v>154</v>
-      </c>
-      <c r="H78" t="s">
-        <v>13</v>
-      </c>
-      <c r="K78" t="s">
-        <v>154</v>
-      </c>
-      <c r="L78" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B79" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" t="s">
-        <v>155</v>
-      </c>
-      <c r="F79" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" t="s">
-        <v>156</v>
-      </c>
-      <c r="H79" t="s">
-        <v>13</v>
-      </c>
-      <c r="K79" t="s">
-        <v>156</v>
-      </c>
-      <c r="L79" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B80" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" t="s">
-        <v>9</v>
-      </c>
-      <c r="E80" t="s">
-        <v>157</v>
-      </c>
-      <c r="F80" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" t="s">
-        <v>158</v>
-      </c>
-      <c r="H80" t="s">
-        <v>13</v>
-      </c>
-      <c r="K80" t="s">
-        <v>158</v>
-      </c>
-      <c r="L80" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8D8C61C-1FFD-4CD0-AE30-6999962C81EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{440A7146-088D-4CB5-9DBD-714FA0940896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E6C1D98F-23EA-4F17-A028-CBE2C29670BD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{90867255-77DF-4DFC-BAB6-0212248C7FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -805,7 +805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11784C7-CD43-430C-BE28-3DBFF61ED80E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97B79AF-EAAC-47C5-8E10-B85AC0E26437}">
   <dimension ref="B3:L45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{440A7146-088D-4CB5-9DBD-714FA0940896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAE4754A-BC04-4627-84A2-CC3DB1733346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{90867255-77DF-4DFC-BAB6-0212248C7FB5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6BC56115-924C-4345-B2B5-2DBCA40AB4CA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -805,7 +805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97B79AF-EAAC-47C5-8E10-B85AC0E26437}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EBFAEF-C636-4B3D-98A3-AAB1780D7C19}">
   <dimension ref="B3:L45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
